--- a/doc/docs/卡牌配置.xlsx
+++ b/doc/docs/卡牌配置.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proj\unityProj\Line\doc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A7223D-DE35-423D-8729-905920A2D6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476A8FC8-A18F-41C4-8073-FB10377B9285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="12240" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CardCfg" sheetId="3" r:id="rId1"/>
-    <sheet name="CardType" sheetId="4" r:id="rId2"/>
-    <sheet name="ReleaseMode" sheetId="5" r:id="rId3"/>
+    <sheet name="卡牌配置" sheetId="3" r:id="rId1"/>
+    <sheet name="卡组阶段类型" sheetId="6" r:id="rId2"/>
+    <sheet name="卡牌标签" sheetId="4" r:id="rId3"/>
+    <sheet name="卡牌释放目标" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
   <si>
     <t>Horizontal</t>
   </si>
@@ -50,42 +51,10 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>faceImg#string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>卡面名</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>title#string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>卡牌标题</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>desc#string</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>卡牌描述</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaCost#int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>能量消耗</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>cardType#int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>卡牌类型</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -113,14 +82,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>交易卡</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CardType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>NoTarget</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -133,66 +94,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>enum#CardType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>releaseMode#int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果数组</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>有向效果数组</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>buy_in</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>买入</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>买入200{勇气}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>sell_out</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>卖出</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>卖出200{勇气}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>看涨</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>看跌</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>[]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["Trade/200"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["Trade/-200"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Stock</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -221,75 +122,119 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>情绪卡</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>社交卡</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>药卡</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Medicine</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Social</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Emotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>期待</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>担忧</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>懊悔</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标类型</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不甘</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>忧虑</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>焦急</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>自信</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>releaseEffect#string[]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>drawedEffect#string[]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>afterDrawEffect#string[]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>enum#ReleaseTarget</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>phaseType#int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PhaseType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Action</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动阶段</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易阶段</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum#PhaseType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>releaseTarget#int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardTag</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Future</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>期货</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agreement</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易协议</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lever</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>杠杆</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agitation</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>煽动</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag#int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum#CardTag</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段类型</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放目标类型</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡牌标签</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>key#string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>符号</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>name#string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -697,23 +642,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.53125" customWidth="1"/>
-    <col min="2" max="2" width="16.53125" customWidth="1"/>
-    <col min="3" max="3" width="13.796875" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
-    <col min="5" max="5" width="24.46484375" customWidth="1"/>
-    <col min="6" max="6" width="18.19921875" customWidth="1"/>
-    <col min="7" max="7" width="20.46484375" customWidth="1"/>
-    <col min="8" max="8" width="44.796875" customWidth="1"/>
-    <col min="9" max="9" width="23.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" customWidth="1"/>
+    <col min="6" max="6" width="38.21875" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
+    <col min="8" max="8" width="44.77734375" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29.33203125" customWidth="1"/>
     <col min="11" max="11" width="14.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.46484375" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -725,71 +670,68 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="6" t="s">
-        <v>65</v>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" s="1">
@@ -804,278 +746,131 @@
       <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="I5" s="3">
-        <v>1</v>
-      </c>
+      <c r="I5" s="3"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>1001</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>39</v>
-      </c>
+    <row r="8" spans="1:12" ht="16.8" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>1002</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>1003</v>
-      </c>
+    <row r="9" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
       <c r="B10" s="10"/>
-      <c r="C10" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>1004</v>
-      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>2001</v>
-      </c>
+      <c r="C11" s="1"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
       <c r="B12" s="10"/>
-      <c r="C12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
+      <c r="C12" s="1"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="10"/>
-      <c r="C13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
+      <c r="C13" s="1"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="10"/>
-      <c r="C14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
+      <c r="C14" s="1"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="10"/>
-      <c r="C15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
+      <c r="C15" s="1"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="10"/>
-      <c r="C16" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="10"/>
-      <c r="C17" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="10"/>
-      <c r="C18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
+      <c r="C18" s="1"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="10"/>
       <c r="C19" s="1"/>
@@ -1084,7 +879,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="10"/>
       <c r="C20" s="1"/>
@@ -1092,14 +887,14 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="10"/>
       <c r="C21" s="1"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="10"/>
       <c r="C22" s="1"/>
@@ -1107,7 +902,7 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -1116,7 +911,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="10"/>
       <c r="C24" s="1"/>
@@ -1124,14 +919,14 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="10"/>
       <c r="C25" s="1"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="10"/>
       <c r="C26" s="1"/>
@@ -1146,93 +941,68 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6A18052-01FA-4CE6-9220-D8759AE3B0CA}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5807FC10-FC60-4776-B502-5180A53A47B1}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.86328125" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="13.9" thickTop="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="C8" s="6"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="C7" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -1241,81 +1011,176 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6A18052-01FA-4CE6-9220-D8759AE3B0CA}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="C8" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B93BA456-7997-481A-AF75-6CDC5048F848}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.46484375" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="13.9" thickTop="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="C7" s="6"/>
     </row>
